--- a/交易下文_测试集v1.0输出.xlsx
+++ b/交易下文_测试集v1.0输出.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="137">
   <si>
     <t>con_ID</t>
   </si>
@@ -41,6 +41,12 @@
     <t>CHATSENDTIMEORI</t>
   </si>
   <si>
+    <t>TRADERNAME</t>
+  </si>
+  <si>
+    <t>INTERLOCUTOR</t>
+  </si>
+  <si>
     <t>is_start</t>
   </si>
   <si>
@@ -72,6 +78,9 @@
   </si>
   <si>
     <t>2026-04-29 08:40:13.000</t>
+  </si>
+  <si>
+    <t>刘安琪</t>
   </si>
   <si>
     <t>价格议价、期限调整</t>
@@ -92,9 +101,6 @@
     }
   ]
 }</t>
-  </si>
-  <si>
-    <t>刘安琪</t>
   </si>
   <si>
     <t>隔夜户暂时平了 一会等新的出来我叫你</t>
@@ -823,6 +829,9 @@
     <t>2026-04-29 08:55:53.000</t>
   </si>
   <si>
+    <t>雷城艳</t>
+  </si>
+  <si>
     <t>10e</t>
   </si>
   <si>
@@ -866,9 +875,6 @@
     }
   ]
 }</t>
-  </si>
-  <si>
-    <t>雷城艳</t>
   </si>
   <si>
     <t>你都隔夜都找谁借啊</t>
@@ -1541,13 +1547,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1903,20 +1912,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="3" max="3" width="43.8796296296296" customWidth="1"/>
     <col min="4" max="4" width="19.1574074074074" customWidth="1"/>
-    <col min="5" max="5" width="14.0277777777778" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="9" width="14.0277777777778" customWidth="1"/>
-    <col min="10" max="11" width="44.75" customWidth="1"/>
-    <col min="12" max="12" width="54.8796296296296" customWidth="1"/>
+    <col min="5" max="5" width="15.962962962963" customWidth="1"/>
+    <col min="6" max="6" width="18.462962962963" customWidth="1"/>
+    <col min="7" max="7" width="14.0277777777778" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="9" max="11" width="14.0277777777778" customWidth="1"/>
+    <col min="12" max="13" width="44.75" customWidth="1"/>
+    <col min="14" max="14" width="54.8796296296296" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27" customHeight="1" spans="1:12">
+    <row r="1" ht="27" customHeight="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1929,10 +1940,10 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
@@ -1953,1247 +1964,1481 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" ht="162" customHeight="1" spans="1:12">
-      <c r="A2" s="4">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" ht="162" customHeight="1" spans="1:14">
+      <c r="A2" s="5">
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="4" t="b">
+      <c r="C2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" ht="162" customHeight="1" spans="1:12">
-      <c r="A3" s="4">
+      <c r="H2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" ht="162" customHeight="1" spans="1:14">
+      <c r="A3" s="5">
         <v>4</v>
       </c>
       <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" ht="162" customHeight="1" spans="1:14">
+      <c r="A4" s="5">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="162" customHeight="1" spans="1:14">
+      <c r="A5" s="6">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" ht="162" customHeight="1" spans="1:14">
+      <c r="A6" s="5">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" ht="162" customHeight="1" spans="1:14">
+      <c r="A7" s="5">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" ht="162" customHeight="1" spans="1:14">
+      <c r="A8" s="5">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" ht="162" customHeight="1" spans="1:14">
+      <c r="A9" s="5">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="I9" s="5"/>
+      <c r="J9" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="4" t="b">
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" ht="162" customHeight="1" spans="1:14">
+      <c r="A10" s="5">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" ht="162" customHeight="1" spans="1:12">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="H10" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" ht="351" customHeight="1" spans="1:14">
+      <c r="A11" s="5">
+        <v>6</v>
+      </c>
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" ht="351" customHeight="1" spans="1:14">
+      <c r="A12" s="5">
+        <v>6</v>
+      </c>
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" ht="351" customHeight="1" spans="1:14">
+      <c r="A13" s="5">
+        <v>6</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="N13" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" ht="351" customHeight="1" spans="1:14">
+      <c r="A14" s="5">
+        <v>6</v>
+      </c>
+      <c r="B14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="N14" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" ht="351" customHeight="1" spans="1:14">
+      <c r="A15" s="5">
+        <v>6</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G15" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="N15" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" ht="351" customHeight="1" spans="1:14">
+      <c r="A16" s="5">
+        <v>6</v>
+      </c>
+      <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="N16" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" ht="162" customHeight="1" spans="1:14">
+      <c r="A17" s="5">
+        <v>7</v>
+      </c>
+      <c r="B17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="N17" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" ht="162" customHeight="1" spans="1:14">
+      <c r="A18" s="5">
+        <v>7</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="N18" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" ht="162" customHeight="1" spans="1:14">
+      <c r="A19" s="5">
+        <v>7</v>
+      </c>
+      <c r="B19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="N19" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" ht="162" customHeight="1" spans="1:14">
+      <c r="A20" s="5">
+        <v>7</v>
+      </c>
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G20" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="N20" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" ht="162" customHeight="1" spans="1:14">
+      <c r="A21" s="5">
+        <v>7</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G21" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="N21" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" ht="162" customHeight="1" spans="1:14">
+      <c r="A22" s="5">
+        <v>8</v>
+      </c>
+      <c r="B22" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="G22" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="N22" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" ht="162" customHeight="1" spans="1:14">
+      <c r="A23" s="5">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="G23" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="4" t="b">
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="N23" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" ht="162" customHeight="1" spans="1:14">
+      <c r="A24" s="5">
+        <v>8</v>
+      </c>
+      <c r="B24" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="G24" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="162" customHeight="1" spans="1:12">
-      <c r="A5" s="5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="5" t="b">
+      <c r="H24" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="N24" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" ht="162" customHeight="1" spans="1:14">
+      <c r="A25" s="5">
+        <v>9</v>
+      </c>
+      <c r="B25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G25" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="N25" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="217.5" customHeight="1" spans="1:14">
+      <c r="A26" s="6">
+        <v>9</v>
+      </c>
+      <c r="B26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G26" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" ht="162" customHeight="1" spans="1:12">
-      <c r="A6" s="4">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="H26" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="4" t="b">
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="N26" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="27" ht="162" customHeight="1" spans="1:14">
+      <c r="A27" s="5">
+        <v>9</v>
+      </c>
+      <c r="B27" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G27" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="N27" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="28" ht="162" customHeight="1" spans="1:14">
+      <c r="A28" s="5">
+        <v>9</v>
+      </c>
+      <c r="B28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G28" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" ht="162" customHeight="1" spans="1:12">
-      <c r="A7" s="4">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="4" t="b">
+      <c r="H28" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="N28" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" ht="256.5" customHeight="1" spans="1:14">
+      <c r="A29" s="5">
+        <v>9</v>
+      </c>
+      <c r="B29" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="N29" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="30" ht="256.5" customHeight="1" spans="1:14">
+      <c r="A30" s="5">
+        <v>9</v>
+      </c>
+      <c r="B30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G30" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" ht="162" customHeight="1" spans="1:12">
-      <c r="A8" s="4">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="H30" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="N30" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="31" ht="256.5" customHeight="1" spans="1:14">
+      <c r="A31" s="5">
+        <v>9</v>
+      </c>
+      <c r="B31" t="s">
+        <v>87</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G31" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="N31" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" ht="351" customHeight="1" spans="1:14">
+      <c r="A32" s="6">
+        <v>9</v>
+      </c>
+      <c r="B32" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G32" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="N32" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" ht="351" customHeight="1" spans="1:14">
+      <c r="A33" s="6">
+        <v>9</v>
+      </c>
+      <c r="B33" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G33" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="4" t="b">
+      <c r="I33" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="N33" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" ht="351" customHeight="1" spans="1:14">
+      <c r="A34" s="6">
+        <v>9</v>
+      </c>
+      <c r="B34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G34" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" ht="162" customHeight="1" spans="1:12">
-      <c r="A9" s="4">
-        <v>5</v>
-      </c>
-      <c r="B9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="4" t="b">
+      <c r="H34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="N34" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="35" ht="256.5" customHeight="1" spans="1:14">
+      <c r="A35" s="5">
+        <v>10</v>
+      </c>
+      <c r="B35" t="s">
+        <v>122</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="G35" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" ht="162" customHeight="1" spans="1:12">
-      <c r="A10" s="4">
-        <v>5</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="H35" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" s="4" t="b">
+      <c r="I35" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="N35" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="36" ht="256.5" customHeight="1" spans="1:14">
+      <c r="A36" s="5">
+        <v>10</v>
+      </c>
+      <c r="B36" t="s">
+        <v>125</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="G36" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" ht="351" customHeight="1" spans="1:12">
-      <c r="A11" s="4">
-        <v>6</v>
-      </c>
-      <c r="B11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" ht="351" customHeight="1" spans="1:12">
-      <c r="A12" s="4">
-        <v>6</v>
-      </c>
-      <c r="B12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12" s="4" t="b">
+      <c r="H36" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="N36" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="37" ht="256.5" customHeight="1" spans="1:14">
+      <c r="A37" s="5">
+        <v>10</v>
+      </c>
+      <c r="B37" t="s">
+        <v>122</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="G37" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" ht="351" customHeight="1" spans="1:12">
-      <c r="A13" s="4">
-        <v>6</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="H37" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" s="4" t="b">
+      <c r="I37" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="N37" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" ht="256.5" customHeight="1" spans="1:14">
+      <c r="A38" s="5">
+        <v>10</v>
+      </c>
+      <c r="B38" t="s">
+        <v>122</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="G38" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" ht="351" customHeight="1" spans="1:12">
-      <c r="A14" s="4">
-        <v>6</v>
-      </c>
-      <c r="B14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="4" t="b">
+      <c r="H38" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="J38" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="N38" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="39" ht="256.5" customHeight="1" spans="1:14">
+      <c r="A39" s="5">
+        <v>10</v>
+      </c>
+      <c r="B39" t="s">
+        <v>125</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="G39" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" ht="351" customHeight="1" spans="1:12">
-      <c r="A15" s="4">
-        <v>6</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="H39" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" ht="351" customHeight="1" spans="1:12">
-      <c r="A16" s="4">
-        <v>6</v>
-      </c>
-      <c r="B16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E16" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="L16" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" ht="162" customHeight="1" spans="1:12">
-      <c r="A17" s="4">
-        <v>7</v>
-      </c>
-      <c r="B17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E17" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="L17" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" ht="162" customHeight="1" spans="1:12">
-      <c r="A18" s="4">
-        <v>7</v>
-      </c>
-      <c r="B18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E18" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="L18" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="19" ht="162" customHeight="1" spans="1:12">
-      <c r="A19" s="4">
-        <v>7</v>
-      </c>
-      <c r="B19" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E19" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="L19" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20" ht="162" customHeight="1" spans="1:12">
-      <c r="A20" s="4">
-        <v>7</v>
-      </c>
-      <c r="B20" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E20" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="L20" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="21" ht="162" customHeight="1" spans="1:12">
-      <c r="A21" s="4">
-        <v>7</v>
-      </c>
-      <c r="B21" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E21" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="L21" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="22" ht="162" customHeight="1" spans="1:12">
-      <c r="A22" s="4">
-        <v>8</v>
-      </c>
-      <c r="B22" t="s">
-        <v>76</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E22" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="L22" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="23" ht="162" customHeight="1" spans="1:12">
-      <c r="A23" s="4">
-        <v>8</v>
-      </c>
-      <c r="B23" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E23" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="L23" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="24" ht="162" customHeight="1" spans="1:12">
-      <c r="A24" s="4">
-        <v>8</v>
-      </c>
-      <c r="B24" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E24" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="L24" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="25" ht="162" customHeight="1" spans="1:12">
-      <c r="A25" s="4">
-        <v>9</v>
-      </c>
-      <c r="B25" t="s">
-        <v>85</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E25" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="L25" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" ht="217.5" customHeight="1" spans="1:12">
-      <c r="A26" s="5">
-        <v>9</v>
-      </c>
-      <c r="B26" t="s">
-        <v>18</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E26" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="L26" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="27" ht="162" customHeight="1" spans="1:12">
-      <c r="A27" s="4">
-        <v>9</v>
-      </c>
-      <c r="B27" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E27" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="L27" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="28" ht="162" customHeight="1" spans="1:12">
-      <c r="A28" s="4">
-        <v>9</v>
-      </c>
-      <c r="B28" t="s">
-        <v>18</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E28" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="L28" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="29" ht="256.5" customHeight="1" spans="1:12">
-      <c r="A29" s="4">
-        <v>9</v>
-      </c>
-      <c r="B29" t="s">
-        <v>85</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E29" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="L29" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="30" ht="256.5" customHeight="1" spans="1:12">
-      <c r="A30" s="4">
-        <v>9</v>
-      </c>
-      <c r="B30" t="s">
-        <v>18</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="E30" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="L30" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="31" ht="256.5" customHeight="1" spans="1:12">
-      <c r="A31" s="4">
-        <v>9</v>
-      </c>
-      <c r="B31" t="s">
-        <v>85</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="E31" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="L31" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" ht="351" customHeight="1" spans="1:12">
-      <c r="A32" s="5">
-        <v>9</v>
-      </c>
-      <c r="B32" t="s">
-        <v>85</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E32" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="I32" s="5"/>
-      <c r="J32" s="5"/>
-      <c r="K32" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="L32" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="33" s="1" customFormat="1" ht="351" customHeight="1" spans="1:12">
-      <c r="A33" s="5">
-        <v>9</v>
-      </c>
-      <c r="B33" t="s">
-        <v>85</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="E33" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="I33" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="L33" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="34" s="1" customFormat="1" ht="351" customHeight="1" spans="1:12">
-      <c r="A34" s="5">
-        <v>9</v>
-      </c>
-      <c r="B34" t="s">
-        <v>18</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="E34" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="H34" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="I34" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="L34" s="5" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="35" ht="256.5" customHeight="1" spans="1:12">
-      <c r="A35" s="4">
-        <v>10</v>
-      </c>
-      <c r="B35" t="s">
-        <v>120</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E35" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="L35" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="36" ht="256.5" customHeight="1" spans="1:12">
-      <c r="A36" s="4">
-        <v>10</v>
-      </c>
-      <c r="B36" t="s">
+      <c r="I39" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="J39" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="N39" s="5" t="s">
         <v>128</v>
-      </c>
-      <c r="E36" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="L36" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="37" ht="256.5" customHeight="1" spans="1:12">
-      <c r="A37" s="4">
-        <v>10</v>
-      </c>
-      <c r="B37" t="s">
-        <v>120</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="E37" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="L37" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="38" ht="256.5" customHeight="1" spans="1:12">
-      <c r="A38" s="4">
-        <v>10</v>
-      </c>
-      <c r="B38" t="s">
-        <v>120</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="E38" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="L38" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="39" ht="256.5" customHeight="1" spans="1:12">
-      <c r="A39" s="4">
-        <v>10</v>
-      </c>
-      <c r="B39" t="s">
-        <v>126</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="E39" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
-      <c r="K39" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="L39" s="4" t="s">
-        <v>125</v>
       </c>
     </row>
   </sheetData>
